--- a/data/AIIMS_Cutoff.xlsx
+++ b/data/AIIMS_Cutoff.xlsx
@@ -2,43 +2,200 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22188" windowHeight="9000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AIIMS Cutoff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AIIMS Cutoff'!$A$1:$E$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'AIIMS Cutoff'!$A$1:$F$176</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="166" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="167" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
+      <charset val="134"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +204,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -61,21 +405,264 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -83,14 +670,62 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -443,7 +1078,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -453,38 +1087,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F176"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Degree</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>Institute Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>State Name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>AIR</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
@@ -493,2305 +1133,4905 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, New Delhi</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>47</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="2" t="n">
         <v>686</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, New Delhi</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="2" t="n">
         <v>633</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, New Delhi</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="2" t="n">
         <v>254</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="2" t="n">
         <v>632</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, New Delhi</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="2" t="n">
         <v>644</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="2" t="n">
         <v>614</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, New Delhi</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>Delhi</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="2" t="n">
         <v>1405</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="2" t="n">
         <v>601</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhopal</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
         <v>524</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="2" t="n">
         <v>619</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhopal</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="2" t="n">
         <v>1142</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="2" t="n">
         <v>604</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhopal</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="2" t="n">
         <v>1582</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="2" t="n">
         <v>598</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhopal</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="2" t="n">
         <v>7030</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="2" t="n">
         <v>565</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhopal</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>Madhya Pradesh</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="2" t="n">
         <v>11713</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="2" t="n">
         <v>552</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhubaneswar</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
         <v>765</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="2" t="n">
         <v>611</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhubaneswar</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="2" t="n">
         <v>1017</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="2" t="n">
         <v>606</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhubaneswar</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="2" t="n">
         <v>1086</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="2" t="n">
         <v>605</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhubaneswar</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="2" t="n">
         <v>2010</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="2" t="n">
         <v>593</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bhubaneswar</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="2" t="n">
         <v>14786</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="2" t="n">
         <v>545</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jodhpur</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
         <v>1798</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="2" t="n">
         <v>595</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jodhpur</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="2" t="n">
         <v>2453</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="2" t="n">
         <v>589</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jodhpur</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="2" t="n">
         <v>3066</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="2" t="n">
         <v>584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jodhpur</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="2" t="n">
         <v>19371</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="2" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jodhpur</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="2" t="n">
         <v>42487</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="2" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Raipur</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
         <v>1376</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="2" t="n">
         <v>601</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Raipur</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="2" t="n">
         <v>2016</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="2" t="n">
         <v>593</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Raipur</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="2" t="n">
         <v>2631</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="2" t="n">
         <v>587</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Raipur</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="2" t="n">
         <v>11751</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="2" t="n">
         <v>552</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Raipur</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>Chhattisgarh</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="2" t="n">
         <v>12960</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="2" t="n">
         <v>549</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rishikesh</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
         <v>781</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="2" t="n">
         <v>611</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rishikesh</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="2" t="n">
         <v>1104</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="2" t="n">
         <v>605</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rishikesh</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="2" t="n">
         <v>1715</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="2" t="n">
         <v>595</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rishikesh</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="2" t="n">
         <v>7924</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="2" t="n">
         <v>562</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rishikesh</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="2" t="n">
         <v>7835</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="2" t="n">
         <v>562</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Patna</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
         <v>1907</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="2" t="n">
         <v>594</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Patna</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="2" t="n">
         <v>2540</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="2" t="n">
         <v>588</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Patna</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="2" t="n">
         <v>3028</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="2" t="n">
         <v>584</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Patna</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="2" t="n">
         <v>17167</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="2" t="n">
         <v>541</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Patna</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
         <is>
           <t>Bihar</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="2" t="n">
         <v>30313</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="2" t="n">
         <v>523</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Nagpur</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
         <v>891</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="2" t="n">
         <v>609</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Nagpur</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="C38" s="2" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="2" t="n">
         <v>1377</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="2" t="n">
         <v>601</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Nagpur</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="2" t="n">
         <v>2923</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="2" t="n">
         <v>592</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Nagpur</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="2" t="n">
         <v>8697</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="2" t="n">
         <v>560</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Nagpur</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Maharashtra</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="2" t="n">
         <v>16192</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="2" t="n">
         <v>542</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Mangalagiri</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
         <v>706</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="2" t="n">
         <v>614</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Mangalagiri</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="2" t="n">
         <v>2575</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="2" t="n">
         <v>588</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Mangalagiri</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="2" t="n">
         <v>2924</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="2" t="n">
         <v>585</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Mangalagiri</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="2" t="n">
         <v>15552</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="2" t="n">
         <v>544</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Mangalagiri</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
         <is>
           <t>Andhra Pradesh</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="2" t="n">
         <v>31007</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="2" t="n">
         <v>521</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bathinda</t>
         </is>
       </c>
-      <c r="B47" s="3" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
         <v>1798</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="2" t="n">
         <v>595</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bathinda</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="2" t="n">
         <v>2453</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="2" t="n">
         <v>589</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bathinda</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="2" t="n">
         <v>3066</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="2" t="n">
         <v>584</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bathinda</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="2" t="n">
         <v>19371</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="2" t="n">
         <v>538</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bathinda</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="2" t="n">
         <v>42487</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="2" t="n">
         <v>510</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Deogarh</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
         <v>3586</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="2" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Deogarh</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="2" t="n">
         <v>4463</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="2" t="n">
         <v>576</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Deogarh</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="2" t="n">
         <v>4672</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="2" t="n">
         <v>575</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Deogarh</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="2" t="n">
         <v>36168</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="2" t="n">
         <v>516</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Deogarh</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
         <is>
           <t>Jharkhand</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="2" t="n">
         <v>59983</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="2" t="n">
         <v>494</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Gorakhpur</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
         <v>2552</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="2" t="n">
         <v>588</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Gorakhpur</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="2" t="n">
         <v>3151</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="2" t="n">
         <v>583</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Gorakhpur</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="E59" s="2" t="n">
         <v>3355</v>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="F59" s="2" t="n">
         <v>582</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Gorakhpur</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="2" t="n">
         <v>26906</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="2" t="n">
         <v>527</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Gorakhpur</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="E61" s="2" t="n">
         <v>46911</v>
       </c>
-      <c r="E61" s="3" t="n">
+      <c r="F61" s="2" t="n">
         <v>506</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Kalyani</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
         <v>2417</v>
       </c>
-      <c r="E62" s="3" t="n">
+      <c r="F62" s="2" t="n">
         <v>589</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Kalyani</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="E63" s="2" t="n">
         <v>3861</v>
       </c>
-      <c r="E63" s="3" t="n">
+      <c r="F63" s="2" t="n">
         <v>579</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Kalyani</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="E64" s="2" t="n">
         <v>4703</v>
       </c>
-      <c r="E64" s="3" t="n">
+      <c r="F64" s="2" t="n">
         <v>574</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Kalyani</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="E65" s="2" t="n">
         <v>17680</v>
       </c>
-      <c r="E65" s="3" t="n">
+      <c r="F65" s="2" t="n">
         <v>540</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Kalyani</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="E66" s="2" t="n">
         <v>58762</v>
       </c>
-      <c r="E66" s="3" t="n">
+      <c r="F66" s="2" t="n">
         <v>495</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rai Bareli</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
         <v>3284</v>
       </c>
-      <c r="E67" s="3" t="n">
+      <c r="F67" s="2" t="n">
         <v>582</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rai Bareli</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="E68" s="2" t="n">
         <v>3545</v>
       </c>
-      <c r="E68" s="3" t="n">
+      <c r="F68" s="2" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rai Bareli</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="E69" s="2" t="n">
         <v>3918</v>
       </c>
-      <c r="E69" s="3" t="n">
+      <c r="F69" s="2" t="n">
         <v>578</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rai Bareli</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="E70" s="2" t="n">
         <v>33926</v>
       </c>
-      <c r="E70" s="3" t="n">
+      <c r="F70" s="2" t="n">
         <v>519</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rai Bareli</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="E71" s="2" t="n">
         <v>49630</v>
       </c>
-      <c r="E71" s="3" t="n">
+      <c r="F71" s="2" t="n">
         <v>503</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bibi Nagar</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
         <v>1793</v>
       </c>
-      <c r="E72" s="3" t="n">
+      <c r="F72" s="2" t="n">
         <v>595</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bibi Nagar</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="E73" s="2" t="n">
         <v>3191</v>
       </c>
-      <c r="E73" s="3" t="n">
+      <c r="F73" s="2" t="n">
         <v>583</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bibi Nagar</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="E74" s="2" t="n">
         <v>4225</v>
       </c>
-      <c r="E74" s="3" t="n">
+      <c r="F74" s="2" t="n">
         <v>577</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bibi Nagar</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="E75" s="2" t="n">
         <v>17480</v>
       </c>
-      <c r="E75" s="3" t="n">
+      <c r="F75" s="2" t="n">
         <v>541</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bibi Nagar</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="C76" s="2" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="E76" s="2" t="n">
         <v>45033</v>
       </c>
-      <c r="E76" s="3" t="n">
+      <c r="F76" s="2" t="n">
         <v>507</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jammu</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="C77" s="2" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
         <v>3898</v>
       </c>
-      <c r="E77" s="3" t="n">
+      <c r="F77" s="2" t="n">
         <v>578</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jammu</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="C78" s="2" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="E78" s="2" t="n">
         <v>4314</v>
       </c>
-      <c r="E78" s="3" t="n">
+      <c r="F78" s="2" t="n">
         <v>576</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jammu</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="C79" s="2" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="E79" s="2" t="n">
         <v>4945</v>
       </c>
-      <c r="E79" s="3" t="n">
+      <c r="F79" s="2" t="n">
         <v>573</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jammu</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="E80" s="2" t="n">
         <v>36367</v>
       </c>
-      <c r="E80" s="3" t="n">
+      <c r="F80" s="2" t="n">
         <v>516</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Jammu</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>Jammu and Kashmir</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="E81" s="2" t="n">
         <v>43200</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="F81" s="2" t="n">
         <v>508</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Guwahati</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="n">
         <v>4016</v>
       </c>
-      <c r="E82" s="3" t="n">
+      <c r="F82" s="2" t="n">
         <v>578</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Guwahati</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="C83" s="2" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="E83" s="2" t="n">
         <v>4708</v>
       </c>
-      <c r="E83" s="3" t="n">
+      <c r="F83" s="2" t="n">
         <v>574</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Guwahati</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="C84" s="2" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="E84" s="2" t="n">
         <v>5463</v>
       </c>
-      <c r="E84" s="3" t="n">
+      <c r="F84" s="2" t="n">
         <v>571</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Guwahati</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="E85" s="2" t="n">
         <v>32675</v>
       </c>
-      <c r="E85" s="3" t="n">
+      <c r="F85" s="2" t="n">
         <v>520</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Guwahati</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="C86" s="2" t="inlineStr">
         <is>
           <t>Assam</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="E86" s="2" t="n">
         <v>55652</v>
       </c>
-      <c r="E86" s="3" t="n">
+      <c r="F86" s="2" t="n">
         <v>498</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rajkot</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="C87" s="2" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
         <v>2642</v>
       </c>
-      <c r="E87" s="3" t="n">
+      <c r="F87" s="2" t="n">
         <v>587</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rajkot</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="C88" s="2" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="E88" s="2" t="n">
         <v>3287</v>
       </c>
-      <c r="E88" s="3" t="n">
+      <c r="F88" s="2" t="n">
         <v>582</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rajkot</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="E89" s="2" t="n">
         <v>3215</v>
       </c>
-      <c r="E89" s="3" t="n">
+      <c r="F89" s="2" t="n">
         <v>582</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rajkot</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="C90" s="2" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="E90" s="2" t="n">
         <v>30407</v>
       </c>
-      <c r="E90" s="3" t="n">
+      <c r="F90" s="2" t="n">
         <v>523</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Rajkot</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="C91" s="2" t="inlineStr">
         <is>
           <t>Gujarat</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="E91" s="2" t="n">
         <v>48673</v>
       </c>
-      <c r="E91" s="3" t="n">
+      <c r="F91" s="2" t="n">
         <v>504</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bilaspur</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="C92" s="2" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="n">
         <v>2486</v>
       </c>
-      <c r="E92" s="3" t="n">
+      <c r="F92" s="2" t="n">
         <v>589</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bilaspur</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="C93" s="2" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="E93" s="2" t="n">
         <v>3153</v>
       </c>
-      <c r="E93" s="3" t="n">
+      <c r="F93" s="2" t="n">
         <v>583</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bilaspur</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="C94" s="2" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="E94" s="2" t="n">
         <v>3666</v>
       </c>
-      <c r="E94" s="3" t="n">
+      <c r="F94" s="2" t="n">
         <v>580</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bilaspur</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="E95" s="2" t="n">
         <v>24786</v>
       </c>
-      <c r="E95" s="3" t="n">
+      <c r="F95" s="2" t="n">
         <v>530</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Bilaspur</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="C96" s="2" t="inlineStr">
         <is>
           <t>Himachal Pradesh</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="E96" s="2" t="n">
         <v>41195</v>
       </c>
-      <c r="E96" s="3" t="n">
+      <c r="F96" s="2" t="n">
         <v>511</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Madurai</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="C97" s="2" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n">
         <v>5394</v>
       </c>
-      <c r="E97" s="3" t="n">
+      <c r="F97" s="2" t="n">
         <v>571</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Madurai</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>OBC</t>
         </is>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="E98" s="2" t="n">
         <v>6456</v>
       </c>
-      <c r="E98" s="3" t="n">
+      <c r="F98" s="2" t="n">
         <v>567</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Madurai</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="E99" s="2" t="n">
         <v>7417</v>
       </c>
-      <c r="E99" s="3" t="n">
+      <c r="F99" s="2" t="n">
         <v>564</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Madurai</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="C100" s="2" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>SC</t>
         </is>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="E100" s="2" t="n">
         <v>43997</v>
       </c>
-      <c r="E100" s="3" t="n">
+      <c r="F100" s="2" t="n">
         <v>508</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
           <t>AIIMS, Madurai</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="C101" s="2" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>ST</t>
         </is>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="E101" s="2" t="n">
         <v>63398</v>
       </c>
-      <c r="E101" s="3" t="n">
+      <c r="F101" s="2" t="n">
         <v>492</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Bathinda ,Jodhpur Romana near Giani Zail Singh College Mandi Dabwali Road Bathinda, Punjab, 151001</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>268965</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Bathinda ,Jodhpur Romana near Giani Zail Singh College Mandi Dabwali Road Bathinda, Punjab, 151001</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>174486</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Bathinda ,Jodhpur Romana near Giani Zail Singh College Mandi Dabwali Road Bathinda, Punjab, 151001</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>536109</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Bilaspur Changar Palasiyan, Himachal Pradesh,All India Institute of Medical Sciences AIIMS Bilaspur Kothipura BILASPUR Himachal Pradesh 174001, Himachal Pradesh, 174001</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>330044</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Bilaspur Changar Palasiyan, Himachal Pradesh,All India Institute of Medical Sciences AIIMS Bilaspur Kothipura BILASPUR Himachal Pradesh 174001, Himachal Pradesh, 174001</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>241346</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Bilaspur Changar Palasiyan, Himachal Pradesh,All India Institute of Medical Sciences AIIMS Bilaspur Kothipura BILASPUR Himachal Pradesh 174001, Himachal Pradesh, 174001</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>486740</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Guwahati,PO-CHANGSARI, DISTRICT-KAMRUP, Assam, 781101</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>340348</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Guwahati,PO-CHANGSARI, DISTRICT-KAMRUP, Assam, 781101</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>309667</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Guwahati,PO-CHANGSARI, DISTRICT-KAMRUP, Assam, 781101</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>730492</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Jammu,AIIMS, Vijaypur, Jammu, Jammu and Kashmir, Jammu And Kashmir, 181134</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Jammu And Kashmir</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>440047</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Jammu,AIIMS, Vijaypur, Jammu, Jammu and Kashmir, Jammu And Kashmir, 181134</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Jammu And Kashmir</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>354680</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Jammu,AIIMS, Vijaypur, Jammu, Jammu and Kashmir, Jammu And Kashmir, 181134</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Jammu And Kashmir</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>221837</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Jammu,AIIMS, Vijaypur, Jammu, Jammu and Kashmir, Jammu And Kashmir, 181134</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Jammu And Kashmir</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>518444</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Jammu,AIIMS, Vijaypur, Jammu, Jammu and Kashmir, Jammu And Kashmir, 181134</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>Jammu And Kashmir</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>770273</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Mangalagiri ,ALL INDIA INSTITUTE OF MEDICAL SCIENCES NEAR TADEPALLI MANGALAGIRI GUNTUR (Dt) ANDHRA PRADESH, Andhra Pradesh, 522503</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>426233</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Mangalagiri ,ALL INDIA INSTITUTE OF MEDICAL SCIENCES NEAR TADEPALLI MANGALAGIRI GUNTUR (Dt) ANDHRA PRADESH, Andhra Pradesh, 522503</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>401069</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Mangalagiri ,ALL INDIA INSTITUTE OF MEDICAL SCIENCES NEAR TADEPALLI MANGALAGIRI GUNTUR (Dt) ANDHRA PRADESH, Andhra Pradesh, 522503</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>279531</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Mangalagiri ,ALL INDIA INSTITUTE OF MEDICAL SCIENCES NEAR TADEPALLI MANGALAGIRI GUNTUR (Dt) ANDHRA PRADESH, Andhra Pradesh, 522503</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>630186</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Rajkot,Admission cell, Academic section, First floor, Academic block, Permanent Campus, AIIMS Rajkot, Khand, Gujarat, 360110</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>392062</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Rajkot,Admission cell, Academic section, First floor, Academic block, Permanent Campus, AIIMS Rajkot, Khand, Gujarat, 360110</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>321581</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS Rajkot,Admission cell, Academic section, First floor, Academic block, Permanent Campus, AIIMS Rajkot, Khand, Gujarat, 360110</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>229985</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bhubaneswar,AT - Sijua, POST - DUMUDUMA, BHUBANESWAR-751019, Odisha, 751019</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>271852</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bhubaneswar,AT - Sijua, POST - DUMUDUMA, BHUBANESWAR-751019, Odisha, 751019</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>241313</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bhubaneswar,AT - Sijua, POST - DUMUDUMA, BHUBANESWAR-751019, Odisha, 751019</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>22426</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bhubaneswar,AT - Sijua, POST - DUMUDUMA, BHUBANESWAR-751019, Odisha, 751019</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>207160</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bhubaneswar,AT - Sijua, POST - DUMUDUMA, BHUBANESWAR-751019, Odisha, 751019</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>781610</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bibi Nagar, Hyderabad,AIIMS Bibinagar (Hyderabad Metropolitan Region) Telangana 508126, Telangana, 508126</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>273253</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bibi Nagar, Hyderabad,AIIMS Bibinagar (Hyderabad Metropolitan Region) Telangana 508126, Telangana, 508126</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>258759</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bibi Nagar, Hyderabad,AIIMS Bibinagar (Hyderabad Metropolitan Region) Telangana 508126, Telangana, 508126</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>221694</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Bibi Nagar, Hyderabad,AIIMS Bibinagar (Hyderabad Metropolitan Region) Telangana 508126, Telangana, 508126</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>225964</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Deogarh ,AIIMS Deoghar Devipur, Jharkhand India, PIN - 814152, Jharkhand, 814152</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>376997</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Deogarh ,AIIMS Deoghar Devipur, Jharkhand India, PIN - 814152, Jharkhand, 814152</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>305719</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Deogarh ,AIIMS Deoghar Devipur, Jharkhand India, PIN - 814152, Jharkhand, 814152</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>534447</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Gorakhpur ,AIIMS Gorakhpur, Medical College Building, Kunraghat, Gorakhpur, Uttar Pradesh, 273008</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>396329</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Gorakhpur ,AIIMS Gorakhpur, Medical College Building, Kunraghat, Gorakhpur, Uttar Pradesh, 273008</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>338406</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Gorakhpur ,AIIMS Gorakhpur, Medical College Building, Kunraghat, Gorakhpur, Uttar Pradesh, 273008</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>294578</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Gorakhpur ,AIIMS Gorakhpur, Medical College Building, Kunraghat, Gorakhpur, Uttar Pradesh, 273008</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>596639</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Jodhpur,BASNI PHASE - II, JODHPUR-342005, Rajasthan, 342005</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>121786</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Jodhpur,BASNI PHASE - II, JODHPUR-342005, Rajasthan, 342005</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>98647</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Jodhpur,BASNI PHASE - II, JODHPUR-342005, Rajasthan, 342005</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>87801</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Jodhpur,BASNI PHASE - II, JODHPUR-342005, Rajasthan, 342005</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>234585</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Jodhpur,BASNI PHASE - II, JODHPUR-342005, Rajasthan, 342005</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>826710</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Kalyani,NH-34 Connector, Basantapur, Saguna, Kalyani, 741245, West Bengal, India, West Bengal, 741245</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>503151</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Kalyani,NH-34 Connector, Basantapur, Saguna, Kalyani, 741245, West Bengal, India, West Bengal, 741245</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>386570</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Kalyani,NH-34 Connector, Basantapur, Saguna, Kalyani, 741245, West Bengal, India, West Bengal, 741245</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>262176</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Kalyani,NH-34 Connector, Basantapur, Saguna, Kalyani, 741245, West Bengal, India, West Bengal, 741245</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>671008</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Kalyani,NH-34 Connector, Basantapur, Saguna, Kalyani, 741245, West Bengal, India, West Bengal, 741245</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>412250</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Madurai,AIIMS MADURAI, Tamil Nadu, 625008</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>409125</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Madurai,AIIMS MADURAI, Tamil Nadu, 625008</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>190373</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Nagpur,PLOT NO 2 SECTOR 20 MIHAN NAGPUR, Maharashtra, 441108</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>339955</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Nagpur,PLOT NO 2 SECTOR 20 MIHAN NAGPUR, Maharashtra, 441108</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>168613</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Nagpur,PLOT NO 2 SECTOR 20 MIHAN NAGPUR, Maharashtra, 441108</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>137288</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Nagpur,PLOT NO 2 SECTOR 20 MIHAN NAGPUR, Maharashtra, 441108</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>197744</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, New Delhi,AIIMS ANSARI NAGAR EAST AUROBINDO MARG NEW DELHI 110029, Delhi (NCT), 110029</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>31622</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, New Delhi,AIIMS ANSARI NAGAR EAST AUROBINDO MARG NEW DELHI 110029, Delhi (NCT), 110029</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>4801</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, New Delhi,AIIMS ANSARI NAGAR EAST AUROBINDO MARG NEW DELHI 110029, Delhi (NCT), 110029</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>296155</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Patna,Phulwarisharif, Patna, Bihar-801507, Bihar, 801507</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>324957</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Patna,Phulwarisharif, Patna, Bihar-801507, Bihar, 801507</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>221737</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Patna,Phulwarisharif, Patna, Bihar-801507, Bihar, 801507</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>436764</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Patna,Phulwarisharif, Patna, Bihar-801507, Bihar, 801507</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>856041</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Rai Bareli ,All India Institute of Medical Sciences Raebareli, Uttar Pradesh, 229405</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>354913</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Rai Bareli ,All India Institute of Medical Sciences Raebareli, Uttar Pradesh, 229405</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>327221</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Rai Bareli ,All India Institute of Medical Sciences Raebareli, Uttar Pradesh, 229405</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>376229</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Rai Bareli ,All India Institute of Medical Sciences Raebareli, Uttar Pradesh, 229405</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>1057165</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Raipur,Tatibandh, G E Road, Raipur Chhattisgarh, Pin - 492099, Chhattisgarh, 492099</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>371868</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Raipur,Tatibandh, G E Road, Raipur Chhattisgarh, Pin - 492099, Chhattisgarh, 492099</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>306492</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Raipur,Tatibandh, G E Road, Raipur Chhattisgarh, Pin - 492099, Chhattisgarh, 492099</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>194869</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Raipur,Tatibandh, G E Road, Raipur Chhattisgarh, Pin - 492099, Chhattisgarh, 492099</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>230742</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Rishikesh ,ALL INDIA INSTITUTE OF MEDICAL SCIENCES, RISHIKESH Uttarakhand - 249203, Uttarakhand, 249203</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>161370</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS, Rishikesh ,ALL INDIA INSTITUTE OF MEDICAL SCIENCES, RISHIKESH Uttarakhand - 249203, Uttarakhand, 249203</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>147945</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS-Bhopal,,SAKET NAGAR BHOPAL, Madhya Pradesh, 462020</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>EWS PwD</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>119885</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS-Bhopal,,SAKET NAGAR BHOPAL, Madhya Pradesh, 462020</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>OBC PwD</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="n">
+        <v>116547</v>
+      </c>
+      <c r="F173" s="2" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS-Bhopal,,SAKET NAGAR BHOPAL, Madhya Pradesh, 462020</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Open PwD</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="n">
+        <v>116405</v>
+      </c>
+      <c r="F174" s="2" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS-Bhopal,,SAKET NAGAR BHOPAL, Madhya Pradesh, 462020</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>SC PwD</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="n">
+        <v>261657</v>
+      </c>
+      <c r="F175" s="2" t="n">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>MBBS</t>
+        </is>
+      </c>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>AIIMS-Bhopal,,SAKET NAGAR BHOPAL, Madhya Pradesh, 462020</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>ST PwD</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="n">
+        <v>636315</v>
+      </c>
+      <c r="F176" s="2" t="n">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E101"/>
+  <autoFilter ref="A1:F176"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/AIIMS_Cutoff.xlsx
+++ b/data/AIIMS_Cutoff.xlsx
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>686</v>
+        <v>695</v>
       </c>
     </row>
     <row r="3">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>633</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4">
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>254</v>
+        <v>292</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>632</v>
+        <v>680</v>
       </c>
     </row>
     <row r="5">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>644</v>
+        <v>793</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>614</v>
+        <v>662</v>
       </c>
     </row>
     <row r="6">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1405</v>
+        <v>987</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>601</v>
+        <v>658</v>
       </c>
     </row>
     <row r="7">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>524</v>
+        <v>571</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>619</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8">
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1142</v>
+        <v>1084</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>604</v>
+        <v>656</v>
       </c>
     </row>
     <row r="9">
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1582</v>
+        <v>1220</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>598</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10">
@@ -1376,10 +1376,10 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>7030</v>
+        <v>7782</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>565</v>
+        <v>608</v>
       </c>
     </row>
     <row r="11">
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>11713</v>
+        <v>8673</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>552</v>
+        <v>604</v>
       </c>
     </row>
     <row r="12">
@@ -1432,10 +1432,10 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>765</v>
+        <v>664</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>611</v>
+        <v>666</v>
       </c>
     </row>
     <row r="13">
@@ -1460,10 +1460,10 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1017</v>
+        <v>1233</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>606</v>
+        <v>654</v>
       </c>
     </row>
     <row r="14">
@@ -1488,10 +1488,10 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1086</v>
+        <v>1660</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>605</v>
+        <v>647</v>
       </c>
     </row>
     <row r="15">
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2010</v>
+        <v>5396</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>593</v>
+        <v>618</v>
       </c>
     </row>
     <row r="16">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>14786</v>
+        <v>10926</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>545</v>
+        <v>597</v>
       </c>
     </row>
     <row r="17">
@@ -1572,10 +1572,10 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1798</v>
+        <v>344</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>595</v>
+        <v>677</v>
       </c>
     </row>
     <row r="18">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2453</v>
+        <v>714</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>589</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19">
@@ -1628,10 +1628,10 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>3066</v>
+        <v>879</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>584</v>
+        <v>660</v>
       </c>
     </row>
     <row r="20">
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>19371</v>
+        <v>3941</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>538</v>
+        <v>627</v>
       </c>
     </row>
     <row r="21">
@@ -1684,10 +1684,10 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>42487</v>
+        <v>4457</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>510</v>
+        <v>623</v>
       </c>
     </row>
     <row r="22">
@@ -1712,10 +1712,10 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1376</v>
+        <v>1008</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>601</v>
+        <v>657</v>
       </c>
     </row>
     <row r="23">
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2016</v>
+        <v>1683</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>593</v>
+        <v>646</v>
       </c>
     </row>
     <row r="24">
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2631</v>
+        <v>2323</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>587</v>
+        <v>640</v>
       </c>
     </row>
     <row r="25">
@@ -1796,10 +1796,10 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>11751</v>
+        <v>12796</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>552</v>
+        <v>592</v>
       </c>
     </row>
     <row r="26">
@@ -1824,10 +1824,10 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>12960</v>
+        <v>16950</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>549</v>
+        <v>582</v>
       </c>
     </row>
     <row r="27">
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>781</v>
+        <v>537</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>611</v>
+        <v>670</v>
       </c>
     </row>
     <row r="28">
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1104</v>
+        <v>979</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>605</v>
+        <v>658</v>
       </c>
     </row>
     <row r="29">
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1715</v>
+        <v>1089</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>595</v>
+        <v>656</v>
       </c>
     </row>
     <row r="30">
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>7924</v>
+        <v>6429</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>562</v>
+        <v>613</v>
       </c>
     </row>
     <row r="31">
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>7835</v>
+        <v>8532</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>562</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32">
@@ -1992,10 +1992,10 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1907</v>
+        <v>1593</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>594</v>
+        <v>648</v>
       </c>
     </row>
     <row r="33">
@@ -2020,10 +2020,10 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2540</v>
+        <v>2054</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>588</v>
+        <v>642</v>
       </c>
     </row>
     <row r="34">
@@ -2048,10 +2048,10 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3028</v>
+        <v>2675</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>584</v>
+        <v>636</v>
       </c>
     </row>
     <row r="35">
@@ -2076,10 +2076,10 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>17167</v>
+        <v>16709</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>541</v>
+        <v>583</v>
       </c>
     </row>
     <row r="36">
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>30313</v>
+        <v>24984</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>523</v>
+        <v>567</v>
       </c>
     </row>
     <row r="37">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>891</v>
+        <v>792</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>609</v>
+        <v>662</v>
       </c>
     </row>
     <row r="38">
@@ -2160,10 +2160,10 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1377</v>
+        <v>1350</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>601</v>
+        <v>651</v>
       </c>
     </row>
     <row r="39">
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2923</v>
+        <v>1839</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>592</v>
+        <v>645</v>
       </c>
     </row>
     <row r="40">
@@ -2216,10 +2216,10 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>8697</v>
+        <v>8360</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>560</v>
+        <v>606</v>
       </c>
     </row>
     <row r="41">
@@ -2244,10 +2244,10 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>16192</v>
+        <v>13431</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>542</v>
+        <v>591</v>
       </c>
     </row>
     <row r="42">
@@ -2272,10 +2272,10 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>706</v>
+        <v>1314</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>614</v>
+        <v>652</v>
       </c>
     </row>
     <row r="43">
@@ -2300,10 +2300,10 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2575</v>
+        <v>2079</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>588</v>
+        <v>642</v>
       </c>
     </row>
     <row r="44">
@@ -2328,10 +2328,10 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>2924</v>
+        <v>3021</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>585</v>
+        <v>634</v>
       </c>
     </row>
     <row r="45">
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>15552</v>
+        <v>16901</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>544</v>
+        <v>582</v>
       </c>
     </row>
     <row r="46">
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>31007</v>
+        <v>21776</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>521</v>
+        <v>573</v>
       </c>
     </row>
     <row r="47">
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1798</v>
+        <v>1630</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>595</v>
+        <v>647</v>
       </c>
     </row>
     <row r="48">
@@ -2440,10 +2440,10 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>2453</v>
+        <v>2190</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>589</v>
+        <v>641</v>
       </c>
     </row>
     <row r="49">
@@ -2468,10 +2468,10 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>3066</v>
+        <v>2910</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>584</v>
+        <v>635</v>
       </c>
     </row>
     <row r="50">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>19371</v>
+        <v>18819</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="51">
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>42487</v>
+        <v>26664</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>510</v>
+        <v>565</v>
       </c>
     </row>
     <row r="52">
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>3586</v>
+        <v>3090</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>580</v>
+        <v>633</v>
       </c>
     </row>
     <row r="53">
@@ -2580,10 +2580,10 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>4463</v>
+        <v>3771</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>576</v>
+        <v>628</v>
       </c>
     </row>
     <row r="54">
@@ -2608,10 +2608,10 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>4672</v>
+        <v>4569</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>575</v>
+        <v>623</v>
       </c>
     </row>
     <row r="55">
@@ -2636,10 +2636,10 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>36168</v>
+        <v>25371</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>516</v>
+        <v>567</v>
       </c>
     </row>
     <row r="56">
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>59983</v>
+        <v>40599</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>494</v>
+        <v>546</v>
       </c>
     </row>
     <row r="57">
@@ -2692,10 +2692,10 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2552</v>
+        <v>2114</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>588</v>
+        <v>642</v>
       </c>
     </row>
     <row r="58">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>3151</v>
+        <v>2443</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>583</v>
+        <v>639</v>
       </c>
     </row>
     <row r="59">
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>3355</v>
+        <v>3085</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>582</v>
+        <v>633</v>
       </c>
     </row>
     <row r="60">
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>26906</v>
+        <v>19159</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>527</v>
+        <v>578</v>
       </c>
     </row>
     <row r="61">
@@ -2804,10 +2804,10 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>46911</v>
+        <v>33950</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>506</v>
+        <v>554</v>
       </c>
     </row>
     <row r="62">
@@ -2832,10 +2832,10 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2417</v>
+        <v>2188</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>589</v>
+        <v>641</v>
       </c>
     </row>
     <row r="63">
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>3861</v>
+        <v>3049</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>579</v>
+        <v>634</v>
       </c>
     </row>
     <row r="64">
@@ -2888,10 +2888,10 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>4703</v>
+        <v>3955</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>574</v>
+        <v>627</v>
       </c>
     </row>
     <row r="65">
@@ -2916,10 +2916,10 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>17680</v>
+        <v>18440</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>540</v>
+        <v>579</v>
       </c>
     </row>
     <row r="66">
@@ -2944,10 +2944,10 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>58762</v>
+        <v>37522</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>495</v>
+        <v>550</v>
       </c>
     </row>
     <row r="67">
@@ -2972,10 +2972,10 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>3284</v>
+        <v>2634</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>582</v>
+        <v>637</v>
       </c>
     </row>
     <row r="68">
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>3545</v>
+        <v>3160</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>580</v>
+        <v>632</v>
       </c>
     </row>
     <row r="69">
@@ -3028,10 +3028,10 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>3918</v>
+        <v>3586</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>578</v>
+        <v>629</v>
       </c>
     </row>
     <row r="70">
@@ -3056,10 +3056,10 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>33926</v>
+        <v>22455</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>519</v>
+        <v>572</v>
       </c>
     </row>
     <row r="71">
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>49630</v>
+        <v>35875</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>503</v>
+        <v>552</v>
       </c>
     </row>
     <row r="72">
@@ -3112,10 +3112,10 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>1793</v>
+        <v>1705</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>595</v>
+        <v>646</v>
       </c>
     </row>
     <row r="73">
@@ -3140,10 +3140,10 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>3191</v>
+        <v>2592</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>583</v>
+        <v>637</v>
       </c>
     </row>
     <row r="74">
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>4225</v>
+        <v>3180</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>577</v>
+        <v>632</v>
       </c>
     </row>
     <row r="75">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>17480</v>
+        <v>17543</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>541</v>
+        <v>581</v>
       </c>
     </row>
     <row r="76">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>45033</v>
+        <v>28792</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>507</v>
+        <v>561</v>
       </c>
     </row>
     <row r="77">
@@ -3252,10 +3252,10 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>3898</v>
+        <v>3327</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>578</v>
+        <v>631</v>
       </c>
     </row>
     <row r="78">
@@ -3280,10 +3280,10 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>4314</v>
+        <v>3834</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>576</v>
+        <v>627</v>
       </c>
     </row>
     <row r="79">
@@ -3308,10 +3308,10 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>4945</v>
+        <v>4748</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>573</v>
+        <v>622</v>
       </c>
     </row>
     <row r="80">
@@ -3336,10 +3336,10 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>36367</v>
+        <v>27322</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>516</v>
+        <v>564</v>
       </c>
     </row>
     <row r="81">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>43200</v>
+        <v>34696</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>508</v>
+        <v>553</v>
       </c>
     </row>
     <row r="82">
@@ -3392,10 +3392,10 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>4016</v>
+        <v>2997</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>578</v>
+        <v>634</v>
       </c>
     </row>
     <row r="83">
@@ -3420,10 +3420,10 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>4708</v>
+        <v>3823</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>574</v>
+        <v>628</v>
       </c>
     </row>
     <row r="84">
@@ -3448,10 +3448,10 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>5463</v>
+        <v>4802</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>571</v>
+        <v>621</v>
       </c>
     </row>
     <row r="85">
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>32675</v>
+        <v>27539</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>520</v>
+        <v>563</v>
       </c>
     </row>
     <row r="86">
@@ -3504,10 +3504,10 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>55652</v>
+        <v>37116</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>498</v>
+        <v>550</v>
       </c>
     </row>
     <row r="87">
@@ -3532,10 +3532,10 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>2642</v>
+        <v>2039</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>587</v>
+        <v>642</v>
       </c>
     </row>
     <row r="88">
@@ -3560,10 +3560,10 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>3287</v>
+        <v>2892</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>582</v>
+        <v>635</v>
       </c>
     </row>
     <row r="89">
@@ -3588,10 +3588,10 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>3215</v>
+        <v>2889</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>582</v>
+        <v>635</v>
       </c>
     </row>
     <row r="90">
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>30407</v>
+        <v>20222</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>523</v>
+        <v>576</v>
       </c>
     </row>
     <row r="91">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>48673</v>
+        <v>31646</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>504</v>
+        <v>557</v>
       </c>
     </row>
     <row r="92">
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>2486</v>
+        <v>2260</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>589</v>
+        <v>640</v>
       </c>
     </row>
     <row r="93">
@@ -3700,10 +3700,10 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>3153</v>
+        <v>2786</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>583</v>
+        <v>636</v>
       </c>
     </row>
     <row r="94">
@@ -3728,10 +3728,10 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>3666</v>
+        <v>3287</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>580</v>
+        <v>632</v>
       </c>
     </row>
     <row r="95">
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24786</v>
+        <v>20129</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>530</v>
+        <v>576</v>
       </c>
     </row>
     <row r="96">
@@ -3784,10 +3784,10 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>41195</v>
+        <v>30805</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>511</v>
+        <v>559</v>
       </c>
     </row>
     <row r="97">
@@ -3812,10 +3812,10 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>5394</v>
+        <v>3421</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>571</v>
+        <v>630</v>
       </c>
     </row>
     <row r="98">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>6456</v>
+        <v>4281</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>567</v>
+        <v>625</v>
       </c>
     </row>
     <row r="99">
@@ -3868,10 +3868,10 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>7417</v>
+        <v>5416</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>564</v>
+        <v>618</v>
       </c>
     </row>
     <row r="100">
@@ -3896,10 +3896,10 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>43997</v>
+        <v>27253</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>508</v>
+        <v>564</v>
       </c>
     </row>
     <row r="101">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>63398</v>
+        <v>44940</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>492</v>
+        <v>541</v>
       </c>
     </row>
     <row r="102">
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>268965</v>
+        <v>225122</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>372</v>
+        <v>421</v>
       </c>
     </row>
     <row r="103">
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>174486</v>
+        <v>211861</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="104">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>536109</v>
+        <v>470951</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>270</v>
+        <v>334</v>
       </c>
     </row>
     <row r="105">
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>330044</v>
+        <v>284684</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>345</v>
+        <v>395</v>
       </c>
     </row>
     <row r="106">
@@ -4064,10 +4064,10 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>241346</v>
+        <v>205434</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>385</v>
+        <v>430</v>
       </c>
     </row>
     <row r="107">
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>486740</v>
+        <v>386020</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>286</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108">
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>340348</v>
+        <v>300462</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>341</v>
+        <v>389</v>
       </c>
     </row>
     <row r="109">
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>309667</v>
+        <v>189156</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>354</v>
+        <v>438</v>
       </c>
     </row>
     <row r="110">
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>730492</v>
+        <v>603010</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>217</v>
+        <v>298</v>
       </c>
     </row>
     <row r="111">
@@ -4204,10 +4204,10 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>440047</v>
+        <v>388651</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>302</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112">
@@ -4232,10 +4232,10 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>354680</v>
+        <v>306676</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>335</v>
+        <v>387</v>
       </c>
     </row>
     <row r="113">
@@ -4260,10 +4260,10 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>221837</v>
+        <v>239506</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>395</v>
+        <v>414</v>
       </c>
     </row>
     <row r="114">
@@ -4288,10 +4288,10 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>518444</v>
+        <v>653328</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="115">
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>770273</v>
+        <v>490090</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>208</v>
+        <v>328</v>
       </c>
     </row>
     <row r="116">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>401069</v>
+        <v>121006</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>316</v>
+        <v>478</v>
       </c>
     </row>
     <row r="118">
@@ -4400,10 +4400,10 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>279531</v>
+        <v>94109</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>367</v>
+        <v>497</v>
       </c>
     </row>
     <row r="119">
@@ -4428,10 +4428,10 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>630186</v>
+        <v>327534</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>243</v>
+        <v>379</v>
       </c>
     </row>
     <row r="120">
@@ -4484,10 +4484,10 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>321581</v>
+        <v>269496</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>349</v>
+        <v>401</v>
       </c>
     </row>
     <row r="122">
@@ -4512,10 +4512,10 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>229985</v>
+        <v>227773</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>391</v>
+        <v>420</v>
       </c>
     </row>
     <row r="123">
@@ -4568,10 +4568,10 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>241313</v>
+        <v>207083</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>385</v>
+        <v>429</v>
       </c>
     </row>
     <row r="125">
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>22426</v>
+        <v>37101</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>533</v>
+        <v>550</v>
       </c>
     </row>
     <row r="126">
@@ -4708,10 +4708,10 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>258759</v>
+        <v>201937</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>377</v>
+        <v>432</v>
       </c>
     </row>
     <row r="130">
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>221694</v>
+        <v>88048</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>395</v>
+        <v>502</v>
       </c>
     </row>
     <row r="131">
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>225964</v>
+        <v>365084</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>393</v>
+        <v>366</v>
       </c>
     </row>
     <row r="132">
@@ -4792,10 +4792,10 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>376997</v>
+        <v>295349</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>326</v>
+        <v>391</v>
       </c>
     </row>
     <row r="133">
@@ -4820,10 +4820,10 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>305719</v>
+        <v>256215</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>356</v>
+        <v>407</v>
       </c>
     </row>
     <row r="134">
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>534447</v>
+        <v>485836</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>271</v>
+        <v>329</v>
       </c>
     </row>
     <row r="135">
@@ -4876,10 +4876,10 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>396329</v>
+        <v>189449</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>318</v>
+        <v>438</v>
       </c>
     </row>
     <row r="136">
@@ -4904,10 +4904,10 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>338406</v>
+        <v>133375</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>341</v>
+        <v>470</v>
       </c>
     </row>
     <row r="137">
@@ -4932,10 +4932,10 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>294578</v>
+        <v>110199</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>361</v>
+        <v>485</v>
       </c>
     </row>
     <row r="138">
@@ -4960,10 +4960,10 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>596639</v>
+        <v>488861</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>252</v>
+        <v>329</v>
       </c>
     </row>
     <row r="139">
@@ -5016,10 +5016,10 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>98647</v>
+        <v>144446</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="141">
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>87801</v>
+        <v>49241</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>473</v>
+        <v>536</v>
       </c>
     </row>
     <row r="142">
@@ -5072,10 +5072,10 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>234585</v>
+        <v>246013</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>389</v>
+        <v>411</v>
       </c>
     </row>
     <row r="143">
@@ -5156,10 +5156,10 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>386570</v>
+        <v>292473</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>322</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146">
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>262176</v>
+        <v>207392</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>375</v>
+        <v>429</v>
       </c>
     </row>
     <row r="147">
@@ -5296,10 +5296,10 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>190373</v>
+        <v>167218</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>411</v>
+        <v>450</v>
       </c>
     </row>
     <row r="151">
@@ -5324,10 +5324,10 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>339955</v>
+        <v>175335</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>341</v>
+        <v>446</v>
       </c>
     </row>
     <row r="152">
@@ -5352,10 +5352,10 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>168613</v>
+        <v>178444</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>423</v>
+        <v>444</v>
       </c>
     </row>
     <row r="153">
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>137288</v>
+        <v>83566</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>442</v>
+        <v>505</v>
       </c>
     </row>
     <row r="154">
@@ -5408,10 +5408,10 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>197744</v>
+        <v>287572</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>408</v>
+        <v>394</v>
       </c>
     </row>
     <row r="155">
@@ -5436,10 +5436,10 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>31622</v>
+        <v>20015</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>521</v>
+        <v>576</v>
       </c>
     </row>
     <row r="156">
@@ -5464,10 +5464,10 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>4801</v>
+        <v>5866</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>574</v>
+        <v>616</v>
       </c>
     </row>
     <row r="157">
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>324957</v>
+        <v>219399</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>347</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159">
@@ -5548,10 +5548,10 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>221737</v>
+        <v>210581</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>395</v>
+        <v>428</v>
       </c>
     </row>
     <row r="160">
@@ -5576,10 +5576,10 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>436764</v>
+        <v>404611</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>303</v>
+        <v>353</v>
       </c>
     </row>
     <row r="161">
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>354913</v>
+        <v>245682</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>335</v>
+        <v>411</v>
       </c>
     </row>
     <row r="163">
@@ -5660,10 +5660,10 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>327221</v>
+        <v>230014</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>346</v>
+        <v>419</v>
       </c>
     </row>
     <row r="164">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>376229</v>
+        <v>528896</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="165">
@@ -5716,10 +5716,10 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>1057165</v>
+        <v>485894</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>151</v>
+        <v>329</v>
       </c>
     </row>
     <row r="166">
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>306492</v>
+        <v>195831</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>355</v>
+        <v>435</v>
       </c>
     </row>
     <row r="168">
@@ -5800,10 +5800,10 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>194869</v>
+        <v>189092</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>409</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169">
@@ -5828,10 +5828,10 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>230742</v>
+        <v>319126</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="170">
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>161370</v>
+        <v>84424</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>427</v>
+        <v>504</v>
       </c>
     </row>
     <row r="171">
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>147945</v>
+        <v>60079</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>435</v>
+        <v>525</v>
       </c>
     </row>
     <row r="172">
@@ -5912,10 +5912,10 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>119885</v>
+        <v>143304</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>452</v>
+        <v>464</v>
       </c>
     </row>
     <row r="173">
@@ -5940,10 +5940,10 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>116547</v>
+        <v>151227</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="174">
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>116405</v>
+        <v>103992</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>454</v>
+        <v>490</v>
       </c>
     </row>
     <row r="175">
@@ -5996,10 +5996,10 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>261657</v>
+        <v>156322</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>376</v>
+        <v>456</v>
       </c>
     </row>
     <row r="176">
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>636315</v>
+        <v>457225</v>
       </c>
       <c r="F176" s="2" t="n">
-        <v>241</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
